--- a/themes/cardQuestion.xlsx
+++ b/themes/cardQuestion.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D7"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -470,101 +470,41 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>75</v>
+        <v>125</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Выпустить цифровую карту можно в приложении «Уралсиб Онлайн» или в веб-версии на [сайте](https://online.uralsib.ru/)</t>
+          <t xml:space="preserve">         Для карт, выданным работодателем, срок активации можно узнать в бухгалтерии организации. </t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t xml:space="preserve">        Выпустить цифровую карту можно в приложении «Уралсиб Онлайн» или в веб-версии на [сайте](https://online.uralsib.ru/).</t>
+          <t xml:space="preserve">         Для карт, выданных работодателем, срок активации можно узнать в бухгалтерии организации. </t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>добавлена точка в конце предложения</t>
+          <t>«выданным» исправлено на «выданных» — согласование падежа с «карт» (родительный падеж)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125</v>
+        <v>130</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Для карт, выданным работодателем, срок активации можно узнать в бухгалтерии организации. </t>
+          <t xml:space="preserve">    reply: Чтобы активировать карту установите PIN-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t xml:space="preserve">         Для карт, выданных работодателем, срок активации можно узнать в бухгалтерии организации. </t>
+          <t xml:space="preserve">    reply: Чтобы активировать карту, установите PIN-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>«выданным» исправлено на «выданных» — согласование падежа с «карт» (родительный падеж)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="n">
-        <v>127</v>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Карта отделений банка доступна [здесь]({{$temp.officeLink}})</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">         Карта отделений банка доступна [здесь]({{$temp.officeLink}}).</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="n">
-        <v>130</v>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reply: Чтобы активировать карту установите PIN-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">    reply: Чтобы активировать карту, установите PIN-код. Для активации бесконтактной оплаты по карте совершите покупку с вводом установленного PIN-кода или запросите баланс в банкомате Уралсиба.</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
           <t>добавлена запятая после придаточного «Чтобы активировать карту»</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>148</v>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для уточнения возможности закрытия заявки на перевыпуск карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">        - Для уточнения возможности закрытия заявки на перевыпуск карты напишите в чат приложения «Уралсиб Онлайн» или его [веб-версии](https://online.uralsib.ru/).</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>добавлена точка в конце предложения</t>
         </is>
       </c>
     </row>
